--- a/examples/example.xlsx
+++ b/examples/example.xlsx
@@ -892,7 +892,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>TEST</v>
+        <v>test</v>
       </c>
       <c r="C13" t="str">
         <v>TEST</v>
